--- a/config/divergent-universe-generated/templates/DivergentUniverseBindings.xlsx
+++ b/config/divergent-universe-generated/templates/DivergentUniverseBindings.xlsx
@@ -19,13 +19,14 @@
     <sheet name="T24_EncounterWaves" sheetId="10" r:id="rId10"/>
     <sheet name="T25_EnemySlots" sheetId="11" r:id="rId11"/>
     <sheet name="T26_BossPools" sheetId="12" r:id="rId12"/>
+    <sheet name="T27_PersonaSourceObligations" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1361" uniqueCount="130">
   <si>
     <t>@table</t>
   </si>
@@ -45,16 +46,16 @@
     <t>id</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>7cd119db777582fe</t>
+    <t>75d54ca0bc085ade</t>
   </si>
   <si>
     <t>#name</t>
@@ -144,7 +145,7 @@
     <t>optional&lt;string&gt;</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
@@ -180,7 +181,7 @@
     <t>DivergentUniverseCurioPoolMembership</t>
   </si>
   <si>
-    <t>cc7e0f1d4f270055</t>
+    <t>d561e5fbbdf53923</t>
   </si>
   <si>
     <t>curio_state_id</t>
@@ -198,7 +199,7 @@
     <t>DivergentUniverseOccurrences</t>
   </si>
   <si>
-    <t>955528d2e29fc624</t>
+    <t>d9549ad1af2e5888</t>
   </si>
   <si>
     <t>variant_ids</t>
@@ -219,7 +220,7 @@
     <t>DivergentUniverseOccurrenceVariants</t>
   </si>
   <si>
-    <t>86b5202416146b0a</t>
+    <t>8163e096d3277972</t>
   </si>
   <si>
     <t>occurrence_id</t>
@@ -243,7 +244,7 @@
     <t>DivergentUniverseOccurrenceChoices</t>
   </si>
   <si>
-    <t>be1734f5280907ee</t>
+    <t>7dc519b0d56d1230</t>
   </si>
   <si>
     <t>variant_id</t>
@@ -264,7 +265,7 @@
     <t>DivergentUniverseModeServiceNpcs</t>
   </si>
   <si>
-    <t>3f08015f240f6a38</t>
+    <t>c7926630ad7a8f96</t>
   </si>
   <si>
     <t>service_kind</t>
@@ -273,7 +274,7 @@
     <t>DivergentUniverseAdventureOutcomes</t>
   </si>
   <si>
-    <t>e969758c7fdc3a22</t>
+    <t>56bad92dc2ed5b5c</t>
   </si>
   <si>
     <t>adventure_type</t>
@@ -288,7 +289,7 @@
     <t>DivergentUniverseEncounterSourceObligations</t>
   </si>
   <si>
-    <t>9caff36f651887a3</t>
+    <t>c623ff39d25df507</t>
   </si>
   <si>
     <t>encounter_group_ids</t>
@@ -309,7 +310,7 @@
     <t>DivergentUniverseEncounterGroups</t>
   </si>
   <si>
-    <t>4bba3e9765d7912a</t>
+    <t>46a872c73996731a</t>
   </si>
   <si>
     <t>module_id</t>
@@ -327,7 +328,7 @@
     <t>DivergentUniverseEncounterWaves</t>
   </si>
   <si>
-    <t>0b7139348892b2ac</t>
+    <t>1ea81fa4ff8db89c</t>
   </si>
   <si>
     <t>enemy_slot_ids</t>
@@ -348,7 +349,7 @@
     <t>DivergentUniverseEnemySlots</t>
   </si>
   <si>
-    <t>50695979c4a83ae9</t>
+    <t>50d0ef1490d47beb</t>
   </si>
   <si>
     <t>wave_id</t>
@@ -372,7 +373,7 @@
     <t>DivergentUniverseBossPools</t>
   </si>
   <si>
-    <t>83266e667b21f524</t>
+    <t>64e96a4916ef9666</t>
   </si>
   <si>
     <t>weekly_modifier_id</t>
@@ -391,6 +392,30 @@
   </si>
   <si>
     <t>optional&lt;ref&lt;DivergentUniverseEncounterGroups.id&gt;&gt;</t>
+  </si>
+  <si>
+    <t>DivergentUniversePersonaSourceObligations</t>
+  </si>
+  <si>
+    <t>c253e4fcb3d1886e</t>
+  </si>
+  <si>
+    <t>source_locator</t>
+  </si>
+  <si>
+    <t>source_key</t>
+  </si>
+  <si>
+    <t>selector_proof</t>
+  </si>
+  <si>
+    <t>parent_sources</t>
+  </si>
+  <si>
+    <t>interpretation</t>
+  </si>
+  <si>
+    <t>runtime_disposition</t>
   </si>
 </sst>
 </file>
@@ -1180,8 +1205,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
@@ -1573,8 +1598,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
@@ -1978,8 +2003,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
@@ -2399,8 +2424,426 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+      <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, ExactOfficialText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="DuEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+      <formula1>"ExactStructured,ExactPublicText,ExactOfficialText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:V7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="3" width="12.7109375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="5" customWidth="1"/>
+    <col min="5" max="8" width="12.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="23.7109375" style="5" customWidth="1"/>
+    <col min="13" max="13" width="32.7109375" style="5" customWidth="1"/>
+    <col min="14" max="14" width="22.7109375" style="5" customWidth="1"/>
+    <col min="15" max="20" width="16.7109375" style="5" customWidth="1"/>
+    <col min="21" max="21" width="19.7109375" style="5" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="24" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="T4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="U4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="T5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="U5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="A6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="42" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+    </row>
+  </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." sqref="B8:B1007">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
@@ -2790,8 +3233,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
@@ -3171,8 +3614,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
@@ -3580,8 +4023,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
@@ -3983,8 +4426,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
@@ -4358,8 +4801,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
@@ -4735,8 +5178,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
@@ -5128,8 +5571,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
@@ -5518,8 +5961,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
